--- a/result/FAT1_LUAD_Tables.xlsx
+++ b/result/FAT1_LUAD_Tables.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EGFRExpression</t>
+          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>-0.120</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.081</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>0.865</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-0.102</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.139</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>0.008</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.904</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.050</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.469</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1566,14 +1566,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.122</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFRExpression</t>
+          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1583,37 +1583,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-0.102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1631,37 +1631,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.081</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>0.865</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.904</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.469</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,21 +1710,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ageG</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.351</v>
+        <v>1.008</v>
       </c>
       <c r="C2" t="n">
-        <v>0.925</v>
+        <v>0.987</v>
       </c>
       <c r="D2" t="n">
-        <v>1.974</v>
+        <v>1.028</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.120</t>
+          <t>0.468</t>
         </is>
       </c>
     </row>
@@ -1741,74 +1741,200 @@
         <v>0.993</v>
       </c>
       <c r="D3" t="n">
-        <v>1.007</v>
+        <v>1.008</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>0.911</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.526</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1.279</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.82</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.104</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FAT1group_Low</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.699</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.478</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.022</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.316</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ALKExpression</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.219</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BRAFExpression</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.138</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FAT1group_Low</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.057</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>gender_MALE</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1.291</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.887</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.188</t>
+      <c r="B9" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.197</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pathologic_stage_2.0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.991</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.181</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.903</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pathologic_stage_4.0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.744</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.624</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.006</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,7 +1981,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
         <v/>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -1886,7 +2012,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -1901,7 +2027,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -1916,7 +2042,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.7016e-02</t>
+          <t>1.3351e-02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -1941,17 +2067,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3213.3559</v>
+        <v>3219.6819</v>
       </c>
       <c r="C8" t="n">
-        <v>533.4832</v>
+        <v>452.8821</v>
       </c>
       <c r="D8" t="n">
-        <v>5893.2287</v>
+        <v>5986.4816</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.023</t>
         </is>
       </c>
     </row>
@@ -1962,138 +2088,126 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>886.8878</v>
+        <v>873.3196</v>
       </c>
       <c r="C9" t="n">
-        <v>70.8257</v>
+        <v>68.21510000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>1702.9499</v>
+        <v>1678.4242</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.034</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-112.9298</v>
+        <v>16.7246</v>
       </c>
       <c r="C10" t="n">
-        <v>-1093.5304</v>
+        <v>-22.5676</v>
       </c>
       <c r="D10" t="n">
-        <v>867.6707</v>
+        <v>56.0169</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0.403</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37.6648</v>
+        <v>-23.5748</v>
       </c>
       <c r="C11" t="n">
-        <v>-1055.287</v>
+        <v>-38.2103</v>
       </c>
       <c r="D11" t="n">
-        <v>1130.6167</v>
+        <v>-8.9392</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.002</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-408.9821</v>
+        <v>-54.2538</v>
       </c>
       <c r="C12" t="n">
-        <v>-2231.0299</v>
+        <v>-482.9274</v>
       </c>
       <c r="D12" t="n">
-        <v>1413.0656</v>
+        <v>374.4198</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>0.804</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>15.8679</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-23.7265</v>
-      </c>
-      <c r="D13" t="n">
-        <v>55.4623</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.431</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-23.4948</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-38.2683</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-8.7212</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
+      <c r="A14">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -2101,12 +2215,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>0.0542</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -2116,12 +2230,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model Formula</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
+          <t>1.1533e-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -2131,14 +2245,10 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0501</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -2146,189 +2256,199 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>9.8815e-03</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2955.3195</v>
+      </c>
+      <c r="C20" t="n">
+        <v>161.7177</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5748.9214</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.038</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>695.8680000000001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-125.6692</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1517.4051</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.097</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_T)[T.2.0]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2572.5561</v>
+        <v>808.4222</v>
       </c>
       <c r="C22" t="n">
-        <v>-81.739</v>
+        <v>-89.3417</v>
       </c>
       <c r="D22" t="n">
-        <v>5226.8512</v>
+        <v>1706.1861</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>0.077</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_T)[T.3.0]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>674.9836</v>
+        <v>1680.3698</v>
       </c>
       <c r="C23" t="n">
-        <v>-138.7654</v>
+        <v>126.3527</v>
       </c>
       <c r="D23" t="n">
-        <v>1488.7327</v>
+        <v>3234.3869</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.034</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.2.0]</t>
+          <t>C(pathologic_T)[T.4.0]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>670.7535</v>
+        <v>1245.1799</v>
       </c>
       <c r="C24" t="n">
-        <v>-197.1179</v>
+        <v>-1040.7184</v>
       </c>
       <c r="D24" t="n">
-        <v>1538.6248</v>
+        <v>3531.0782</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.285</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.3.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1394.003</v>
+        <v>17.7581</v>
       </c>
       <c r="C25" t="n">
-        <v>-69.7958</v>
+        <v>-21.4363</v>
       </c>
       <c r="D25" t="n">
-        <v>2857.8017</v>
+        <v>56.9525</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.373</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.4.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>702.5762999999999</v>
+        <v>-22.7482</v>
       </c>
       <c r="C26" t="n">
-        <v>-1366.6138</v>
+        <v>-37.4154</v>
       </c>
       <c r="D26" t="n">
-        <v>2771.7664</v>
+        <v>-8.081099999999999</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>0.002</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17.8058</v>
+        <v>-273.2395</v>
       </c>
       <c r="C27" t="n">
-        <v>-20.9207</v>
+        <v>-758.1485</v>
       </c>
       <c r="D27" t="n">
-        <v>56.5323</v>
+        <v>211.6696</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.268</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-22.1833</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-36.7615</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-7.6052</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2336,12 +2456,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Model Formula</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_N)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2351,12 +2471,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model Formula</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
+          <t>0.0403</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2366,12 +2486,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R-squared</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>6.7575e-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2381,14 +2501,10 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3.8266e-02</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2396,158 +2512,168 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3232.6531</v>
+      </c>
+      <c r="C35" t="n">
+        <v>360.7059</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6104.6004</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.027</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(gender)[T.MALE]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3288.1598</v>
+        <v>884.1013</v>
       </c>
       <c r="C36" t="n">
-        <v>607.0418</v>
+        <v>59.9918</v>
       </c>
       <c r="D36" t="n">
-        <v>5969.2778</v>
+        <v>1708.2107</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.036</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_N)[T.1.0]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>895.779</v>
+        <v>-481.9716</v>
       </c>
       <c r="C37" t="n">
-        <v>77.5986</v>
+        <v>-1688.4045</v>
       </c>
       <c r="D37" t="n">
-        <v>1713.9594</v>
+        <v>724.4613000000001</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.432</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.1.0]</t>
+          <t>C(pathologic_N)[T.2.0]</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-425.1005</v>
+        <v>-211.7814</v>
       </c>
       <c r="C38" t="n">
-        <v>-1458.1212</v>
+        <v>-1832.1531</v>
       </c>
       <c r="D38" t="n">
-        <v>607.9203</v>
+        <v>1408.5902</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.797</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.2.0]</t>
+          <t>C(pathologic_N)[T.3.0]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-112.3911</v>
+        <v>-984.9736</v>
       </c>
       <c r="C39" t="n">
-        <v>-1268.1791</v>
+        <v>-6218.0168</v>
       </c>
       <c r="D39" t="n">
-        <v>1043.3968</v>
+        <v>4248.0695</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>0.711</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.3.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-885.6362</v>
+        <v>15.9911</v>
       </c>
       <c r="C40" t="n">
-        <v>-5987.0654</v>
+        <v>-24.2847</v>
       </c>
       <c r="D40" t="n">
-        <v>4215.7929</v>
+        <v>56.2669</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.435</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.8961</v>
+        <v>-23.9593</v>
       </c>
       <c r="C41" t="n">
-        <v>-24.0188</v>
+        <v>-38.9108</v>
       </c>
       <c r="D41" t="n">
-        <v>55.811</v>
+        <v>-9.0078</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.002</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>number_pack_years_smoked</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-23.8813</v>
+        <v>51.3778</v>
       </c>
       <c r="C42" t="n">
-        <v>-38.7465</v>
+        <v>-581.8903</v>
       </c>
       <c r="D42" t="n">
-        <v>-9.0161</v>
+        <v>684.6459</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.873</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2686,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
+        <f>== [ Model: Base + Pathologic M ] ===</f>
         <v/>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2591,7 +2717,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_M)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -2606,7 +2732,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.0607</t>
+          <t>0.0675</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2621,7 +2747,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5.7688e-03</t>
+          <t>6.7594e-03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2646,17 +2772,17 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3285.9792</v>
+        <v>2865.775</v>
       </c>
       <c r="C50" t="n">
-        <v>1182.901</v>
+        <v>650.9094</v>
       </c>
       <c r="D50" t="n">
-        <v>5389.0574</v>
+        <v>5080.6405</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.011</t>
         </is>
       </c>
     </row>
@@ -2667,17 +2793,17 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>690.6038</v>
+        <v>646.996</v>
       </c>
       <c r="C51" t="n">
-        <v>38.6094</v>
+        <v>-10.8021</v>
       </c>
       <c r="D51" t="n">
-        <v>1342.5981</v>
+        <v>1304.7942</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.054</t>
         </is>
       </c>
     </row>
@@ -2688,17 +2814,17 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-232.9108</v>
+        <v>-890.1712</v>
       </c>
       <c r="C52" t="n">
-        <v>-1471.3941</v>
+        <v>-2464.8652</v>
       </c>
       <c r="D52" t="n">
-        <v>1005.5724</v>
+        <v>684.5229</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.267</t>
         </is>
       </c>
     </row>
@@ -2709,17 +2835,17 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12.1123</v>
+        <v>11.4403</v>
       </c>
       <c r="C53" t="n">
-        <v>-19.5696</v>
+        <v>-20.3873</v>
       </c>
       <c r="D53" t="n">
-        <v>43.7942</v>
+        <v>43.2679</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>0.480</t>
         </is>
       </c>
     </row>
@@ -2730,13 +2856,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-21.4915</v>
+        <v>-21.002</v>
       </c>
       <c r="C54" t="n">
-        <v>-33.4927</v>
+        <v>-33.0662</v>
       </c>
       <c r="D54" t="n">
-        <v>-9.4903</v>
+        <v>-8.937799999999999</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2745,11 +2871,32 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>280.1824</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-136.7087</v>
+      </c>
+      <c r="D55" t="n">
+        <v>697.0736000000001</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.187</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result/FAT1_LUAD_Tables.xlsx
+++ b/result/FAT1_LUAD_Tables.xlsx
@@ -1677,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1714,17 +1714,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.008</v>
+        <v>1.007</v>
       </c>
       <c r="C2" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
       <c r="D2" t="n">
-        <v>1.028</v>
+        <v>1.027</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.462</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="C3" t="n">
         <v>0.993</v>
@@ -1745,196 +1745,70 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>0.837</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>1.527</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.823</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>FAT1group_Low</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.465</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.050</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.993</v>
+        <v>1.277</v>
       </c>
       <c r="C6" t="n">
-        <v>0.983</v>
+        <v>0.873</v>
       </c>
       <c r="D6" t="n">
-        <v>1.004</v>
+        <v>1.868</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.219</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.138</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FAT1group_Low</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.057</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>gender_MALE</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.298</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.929</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.197</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>pathologic_stage_2.0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.991</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.247</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.181</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pathologic_stage_3.0</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.903</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.805</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.744</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.339</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.624</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.006</t>
+          <t>0.208</t>
         </is>
       </c>
     </row>

--- a/result/FAT1_LUAD_Tables.xlsx
+++ b/result/FAT1_LUAD_Tables.xlsx
@@ -1677,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.472</t>
         </is>
       </c>
     </row>
@@ -1745,70 +1745,112 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.819</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
+          <t>FAT1group_Low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.527</v>
+        <v>0.718</v>
       </c>
       <c r="C4" t="n">
-        <v>1.28</v>
+        <v>0.488</v>
       </c>
       <c r="D4" t="n">
-        <v>1.823</v>
+        <v>1.058</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.094</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FAT1group_Low</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.267</v>
       </c>
       <c r="C5" t="n">
-        <v>0.465</v>
+        <v>0.858</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.050</t>
+          <t>0.234</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>pathologic_stage_2.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.277</v>
+        <v>2.022</v>
       </c>
       <c r="C6" t="n">
-        <v>0.873</v>
+        <v>1.274</v>
       </c>
       <c r="D6" t="n">
-        <v>1.868</v>
+        <v>3.211</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.776</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.572</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pathologic_stage_4.0</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.839</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.758</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.004</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1886,7 +1928,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender)</t>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -1901,7 +1943,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0375</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -1916,7 +1958,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.3351e-02</t>
+          <t>5.6393e-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -1941,17 +1983,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3219.6819</v>
+        <v>3148.8843</v>
       </c>
       <c r="C8" t="n">
-        <v>452.8821</v>
+        <v>569.7424999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>5986.4816</v>
+        <v>5728.0261</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.017</t>
         </is>
       </c>
     </row>
@@ -1962,13 +2004,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>873.3196</v>
+        <v>859.5321</v>
       </c>
       <c r="C9" t="n">
-        <v>68.21510000000001</v>
+        <v>66.7257</v>
       </c>
       <c r="D9" t="n">
-        <v>1678.4242</v>
+        <v>1652.3386</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1983,17 +2025,17 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.7246</v>
+        <v>16.1815</v>
       </c>
       <c r="C10" t="n">
-        <v>-22.5676</v>
+        <v>-22.5151</v>
       </c>
       <c r="D10" t="n">
-        <v>56.0169</v>
+        <v>54.8781</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>0.411</t>
         </is>
       </c>
     </row>
@@ -2004,13 +2046,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-23.5748</v>
+        <v>-23.3686</v>
       </c>
       <c r="C11" t="n">
-        <v>-38.2103</v>
+        <v>-37.8883</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.9392</v>
+        <v>-8.8489</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2019,39 +2061,33 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-54.2538</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-482.9274</v>
-      </c>
-      <c r="D12" t="n">
-        <v>374.4198</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.804</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14">
-        <f>== [ Model: Base + Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -2059,12 +2095,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Model Formula</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -2074,12 +2110,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model Formula</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_T)</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -2089,12 +2125,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R-squared</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.0542</t>
+          <t>4.7016e-02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -2104,14 +2140,10 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.1533e-02</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -2119,195 +2151,193 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3213.3559</v>
+      </c>
+      <c r="C19" t="n">
+        <v>533.4832</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5893.2287</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(gender)[T.MALE]</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2955.3195</v>
+        <v>886.8878</v>
       </c>
       <c r="C20" t="n">
-        <v>161.7177</v>
+        <v>70.8257</v>
       </c>
       <c r="D20" t="n">
-        <v>5748.9214</v>
+        <v>1702.9499</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.033</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_stage)[T.2.0]</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>695.8680000000001</v>
+        <v>-112.9298</v>
       </c>
       <c r="C21" t="n">
-        <v>-125.6692</v>
+        <v>-1093.5304</v>
       </c>
       <c r="D21" t="n">
-        <v>1517.4051</v>
+        <v>867.6707</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.821</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.2.0]</t>
+          <t>C(pathologic_stage)[T.3.0]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>808.4222</v>
+        <v>37.6648</v>
       </c>
       <c r="C22" t="n">
-        <v>-89.3417</v>
+        <v>-1055.287</v>
       </c>
       <c r="D22" t="n">
-        <v>1706.1861</v>
+        <v>1130.6167</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.946</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.3.0]</t>
+          <t>C(pathologic_stage)[T.4.0]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1680.3698</v>
+        <v>-408.9821</v>
       </c>
       <c r="C23" t="n">
-        <v>126.3527</v>
+        <v>-2231.0299</v>
       </c>
       <c r="D23" t="n">
-        <v>3234.3869</v>
+        <v>1413.0656</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.659</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.4.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1245.1799</v>
+        <v>15.8679</v>
       </c>
       <c r="C24" t="n">
-        <v>-1040.7184</v>
+        <v>-23.7265</v>
       </c>
       <c r="D24" t="n">
-        <v>3531.0782</v>
+        <v>55.4623</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0.431</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.7581</v>
+        <v>-23.4948</v>
       </c>
       <c r="C25" t="n">
-        <v>-21.4363</v>
+        <v>-38.2683</v>
       </c>
       <c r="D25" t="n">
-        <v>56.9525</v>
+        <v>-8.7212</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.002</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>-22.7482</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-37.4154</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-8.081099999999999</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>-273.2395</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-758.1485</v>
-      </c>
-      <c r="D27" t="n">
-        <v>211.6696</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.268</t>
-        </is>
-      </c>
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29">
-        <f>== [ Model: Base + Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2315,12 +2345,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>0.0501</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -2330,12 +2360,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model Formula</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_N)</t>
+          <t>9.8815e-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2345,14 +2375,10 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>0.0403</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2360,210 +2386,208 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>6.7575e-02</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2572.5561</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-81.739</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5226.8512</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.057</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>674.9836</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-138.7654</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1488.7327</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_T)[T.2.0]</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3232.6531</v>
+        <v>670.7535</v>
       </c>
       <c r="C35" t="n">
-        <v>360.7059</v>
+        <v>-197.1179</v>
       </c>
       <c r="D35" t="n">
-        <v>6104.6004</v>
+        <v>1538.6248</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.129</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_T)[T.3.0]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>884.1013</v>
+        <v>1394.003</v>
       </c>
       <c r="C36" t="n">
-        <v>59.9918</v>
+        <v>-69.7958</v>
       </c>
       <c r="D36" t="n">
-        <v>1708.2107</v>
+        <v>2857.8017</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.062</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.1.0]</t>
+          <t>C(pathologic_T)[T.4.0]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-481.9716</v>
+        <v>702.5762999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>-1688.4045</v>
+        <v>-1366.6138</v>
       </c>
       <c r="D37" t="n">
-        <v>724.4613000000001</v>
+        <v>2771.7664</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>0.505</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.2.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-211.7814</v>
+        <v>17.8058</v>
       </c>
       <c r="C38" t="n">
-        <v>-1832.1531</v>
+        <v>-20.9207</v>
       </c>
       <c r="D38" t="n">
-        <v>1408.5902</v>
+        <v>56.5323</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>0.366</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.3.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-984.9736</v>
+        <v>-22.1833</v>
       </c>
       <c r="C39" t="n">
-        <v>-6218.0168</v>
+        <v>-36.7615</v>
       </c>
       <c r="D39" t="n">
-        <v>4248.0695</v>
+        <v>-7.6052</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.003</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>15.9911</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-24.2847</v>
-      </c>
-      <c r="D40" t="n">
-        <v>56.2669</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.435</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-23.9593</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-38.9108</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-9.0078</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>51.3778</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-581.8903</v>
-      </c>
-      <c r="D42" t="n">
-        <v>684.6459</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.873</t>
-        </is>
-      </c>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44">
-        <f>== [ Model: Base + Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0404</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -2571,12 +2595,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>3.8266e-02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2586,14 +2610,10 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_M)</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -2601,176 +2621,349 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0675</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3288.1598</v>
+      </c>
+      <c r="C47" t="n">
+        <v>607.0418</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5969.2778</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>6.7594e-03</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>895.779</v>
+      </c>
+      <c r="C48" t="n">
+        <v>77.5986</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1713.9594</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-425.1005</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1458.1212</v>
+      </c>
+      <c r="D49" t="n">
+        <v>607.9203</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.419</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_N)[T.2.0]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2865.775</v>
+        <v>-112.3911</v>
       </c>
       <c r="C50" t="n">
-        <v>650.9094</v>
+        <v>-1268.1791</v>
       </c>
       <c r="D50" t="n">
-        <v>5080.6405</v>
+        <v>1043.3968</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.848</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_N)[T.3.0]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>646.996</v>
+        <v>-885.6362</v>
       </c>
       <c r="C51" t="n">
-        <v>-10.8021</v>
+        <v>-5987.0654</v>
       </c>
       <c r="D51" t="n">
-        <v>1304.7942</v>
+        <v>4215.7929</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.733</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C(pathologic_M)[T.1.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-890.1712</v>
+        <v>15.8961</v>
       </c>
       <c r="C52" t="n">
-        <v>-2464.8652</v>
+        <v>-24.0188</v>
       </c>
       <c r="D52" t="n">
-        <v>684.5229</v>
+        <v>55.811</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>0.434</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>11.4403</v>
+        <v>-23.8813</v>
       </c>
       <c r="C53" t="n">
-        <v>-20.3873</v>
+        <v>-38.7465</v>
       </c>
       <c r="D53" t="n">
-        <v>43.2679</v>
+        <v>-9.0161</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.480</t>
+          <t>0.002</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>-21.002</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-33.0662</v>
-      </c>
-      <c r="D54" t="n">
-        <v>-8.937799999999999</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>280.1824</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-136.7087</v>
-      </c>
-      <c r="D55" t="n">
-        <v>697.0736000000001</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0.187</t>
-        </is>
-      </c>
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0607</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5.7688e-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3285.9792</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1182.901</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5389.0574</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>690.6038</v>
+      </c>
+      <c r="C62" t="n">
+        <v>38.6094</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1342.5981</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.038</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-232.9108</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1471.3941</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1005.5724</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.711</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>12.1123</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-19.5696</v>
+      </c>
+      <c r="D64" t="n">
+        <v>43.7942</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-21.4915</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-33.4927</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-9.4903</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result/FAT1_LUAD_Tables.xlsx
+++ b/result/FAT1_LUAD_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1865,18 +1866,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1896,1074 +1897,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Base Model (No Stage) ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.462</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.837</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.823</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0375</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>FAT1group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.050</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5.6393e-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3148.8843</v>
-      </c>
-      <c r="C8" t="n">
-        <v>569.7424999999999</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5728.0261</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.017</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>859.5321</v>
-      </c>
-      <c r="C9" t="n">
-        <v>66.7257</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1652.3386</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.034</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>16.1815</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-22.5151</v>
-      </c>
-      <c r="D10" t="n">
-        <v>54.8781</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.411</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-23.3686</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-37.8883</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-8.8489</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <f>== [ Model: Base + Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0.0385</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>4.7016e-02</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3213.3559</v>
-      </c>
-      <c r="C19" t="n">
-        <v>533.4832</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5893.2287</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.019</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>886.8878</v>
-      </c>
-      <c r="C20" t="n">
-        <v>70.8257</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1702.9499</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.033</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>-112.9298</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1093.5304</v>
-      </c>
-      <c r="D21" t="n">
-        <v>867.6707</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.821</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>37.6648</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1055.287</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1130.6167</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.946</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-408.9821</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-2231.0299</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1413.0656</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.659</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>15.8679</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-23.7265</v>
-      </c>
-      <c r="D24" t="n">
-        <v>55.4623</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.431</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-23.4948</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-38.2683</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-8.7212</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <f>== [ Model: Base + Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>0.0501</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>9.8815e-03</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2572.5561</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-81.739</v>
-      </c>
-      <c r="D33" t="n">
-        <v>5226.8512</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.057</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>674.9836</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-138.7654</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1488.7327</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0.104</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>670.7535</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-197.1179</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1538.6248</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.129</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1394.003</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-69.7958</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2857.8017</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.062</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>702.5762999999999</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-1366.6138</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2771.7664</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.505</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>17.8058</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-20.9207</v>
-      </c>
-      <c r="D38" t="n">
-        <v>56.5323</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.366</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>-22.1833</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-36.7615</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-7.6052</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <f>== [ Model: Base + Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>0.0404</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3.8266e-02</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3288.1598</v>
-      </c>
-      <c r="C47" t="n">
-        <v>607.0418</v>
-      </c>
-      <c r="D47" t="n">
-        <v>5969.2778</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0.016</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>895.779</v>
-      </c>
-      <c r="C48" t="n">
-        <v>77.5986</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1713.9594</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0.032</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>-425.1005</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-1458.1212</v>
-      </c>
-      <c r="D49" t="n">
-        <v>607.9203</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0.419</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>-112.3911</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1268.1791</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1043.3968</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0.848</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>-885.6362</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-5987.0654</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4215.7929</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.733</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>15.8961</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-24.0188</v>
-      </c>
-      <c r="D52" t="n">
-        <v>55.811</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.434</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-23.8813</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-38.7465</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-9.0161</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <f>== [ Model: Base + Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>0.0607</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>5.7688e-03</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>3285.9792</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1182.901</v>
-      </c>
-      <c r="D61" t="n">
-        <v>5389.0574</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>690.6038</v>
-      </c>
-      <c r="C62" t="n">
-        <v>38.6094</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1342.5981</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0.038</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>-232.9108</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-1471.3941</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1005.5724</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0.711</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>12.1123</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-19.5696</v>
-      </c>
-      <c r="D64" t="n">
-        <v>43.7942</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0.452</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>-21.4915</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-33.4927</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-9.4903</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.868</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.208</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2976,6 +2012,1047 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0375</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5.6393e-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3148.884</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>569.742-5728.026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>859.532</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>66.726-1652.339</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.034</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16.182</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-22.515-54.878</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.411</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-23.369</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-37.888--8.849</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0385</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4.7016e-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3213.356</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>533.483-5893.229</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>886.888</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>70.826-1702.95</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.033</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-112.93</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-1093.53-867.671</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.821</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>37.665</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-1055.287-1130.617</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.946</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-408.982</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-2231.03-1413.066</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.659</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>15.868</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-23.727-55.462</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.431</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-23.495</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-38.268--8.721</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0501</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>9.8815e-03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2572.556</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-81.739-5226.851</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.057</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>674.984</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-138.765-1488.733</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>670.753</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-197.118-1538.625</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.129</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1394.003</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-69.796-2857.802</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.062</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>702.576</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-1366.614-2771.766</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.505</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>17.806</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-20.921-56.532</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.366</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-22.183</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-36.762--7.605</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0404</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3.8266e-02</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3288.16</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>607.042-5969.278</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>895.779</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>77.599-1713.959</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-425.1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-1458.121-607.92</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.419</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>-112.391</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-1268.179-1043.397</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-885.636</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-5987.065-4215.793</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>15.896</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-24.019-55.811</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.434</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-23.881</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-38.746--9.016</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0607</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5.7688e-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3285.979</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1182.901-5389.057</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>690.604</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>38.609-1342.598</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.038</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-232.911</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-1471.394-1005.572</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.711</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>12.112</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-19.57-43.794</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-21.492</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-33.493--9.49</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/FAT1_LUAD_Tables.xlsx
+++ b/result/FAT1_LUAD_Tables.xlsx
@@ -875,27 +875,27 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>EGFRExpression</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -927,27 +927,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.131</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>0.141</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>-0.004</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.017</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.041</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.120</t>
         </is>
       </c>
     </row>
@@ -971,27 +971,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>0.002</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.921</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.700</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.361</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.081</t>
         </is>
       </c>
     </row>
@@ -1023,27 +1023,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-0.016</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1067,27 +1067,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.774</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1119,27 +1119,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>-0.022</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.072</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>-0.048</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-0.050</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1163,34 +1163,34 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.983</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>0.624</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.112</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>0.291</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.265</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1220,22 +1220,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.057</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -1248,45 +1248,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.177</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,42 +1296,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.141</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-0.039</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-0.022</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>-0.004</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.046</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.072</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-0.057</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.067</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.080</t>
         </is>
       </c>
     </row>
@@ -1344,45 +1344,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.078</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,42 +1392,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.048</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.067</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.040</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.003</t>
         </is>
       </c>
     </row>
@@ -1440,45 +1440,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.921</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.940</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>-0.040</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1536,45 +1536,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>0.700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1584,37 +1584,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1632,37 +1632,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.361</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>

--- a/result/FAT1_LUAD_Tables.xlsx
+++ b/result/FAT1_LUAD_Tables.xlsx
@@ -1678,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,15 +1694,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1717,13 +1712,28 @@
       <c r="B2" t="n">
         <v>1.007</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.027</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+FAT1group_Low                          0.488
+gender_MALE                            0.858
+pathologic_stage_2.0                   1.274
+pathologic_stage_3.0                   1.776
+pathologic_stage_4.0                   1.400
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+FAT1group_Low                          1.058
+gender_MALE                            1.870
+pathologic_stage_2.0                   3.211
+pathologic_stage_3.0                   4.572
+pathologic_stage_4.0                   5.758
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.472</t>
         </is>
@@ -1738,13 +1748,28 @@
       <c r="B3" t="n">
         <v>1.001</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+FAT1group_Low                          0.488
+gender_MALE                            0.858
+pathologic_stage_2.0                   1.274
+pathologic_stage_3.0                   1.776
+pathologic_stage_4.0                   1.400
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+FAT1group_Low                          1.058
+gender_MALE                            1.870
+pathologic_stage_2.0                   3.211
+pathologic_stage_3.0                   4.572
+pathologic_stage_4.0                   5.758
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.819</t>
         </is>
@@ -1759,13 +1784,28 @@
       <c r="B4" t="n">
         <v>0.718</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.058</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+FAT1group_Low                          0.488
+gender_MALE                            0.858
+pathologic_stage_2.0                   1.274
+pathologic_stage_3.0                   1.776
+pathologic_stage_4.0                   1.400
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+FAT1group_Low                          1.058
+gender_MALE                            1.870
+pathologic_stage_2.0                   3.211
+pathologic_stage_3.0                   4.572
+pathologic_stage_4.0                   5.758
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.094</t>
         </is>
@@ -1780,13 +1820,28 @@
       <c r="B5" t="n">
         <v>1.267</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+FAT1group_Low                          0.488
+gender_MALE                            0.858
+pathologic_stage_2.0                   1.274
+pathologic_stage_3.0                   1.776
+pathologic_stage_4.0                   1.400
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+FAT1group_Low                          1.058
+gender_MALE                            1.870
+pathologic_stage_2.0                   3.211
+pathologic_stage_3.0                   4.572
+pathologic_stage_4.0                   5.758
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.234</t>
         </is>
@@ -1801,13 +1856,28 @@
       <c r="B6" t="n">
         <v>2.022</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.274</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.211</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+FAT1group_Low                          0.488
+gender_MALE                            0.858
+pathologic_stage_2.0                   1.274
+pathologic_stage_3.0                   1.776
+pathologic_stage_4.0                   1.400
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+FAT1group_Low                          1.058
+gender_MALE                            1.870
+pathologic_stage_2.0                   3.211
+pathologic_stage_3.0                   4.572
+pathologic_stage_4.0                   5.758
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.003</t>
         </is>
@@ -1822,13 +1892,28 @@
       <c r="B7" t="n">
         <v>2.85</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.776</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.572</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+FAT1group_Low                          0.488
+gender_MALE                            0.858
+pathologic_stage_2.0                   1.274
+pathologic_stage_3.0                   1.776
+pathologic_stage_4.0                   1.400
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+FAT1group_Low                          1.058
+gender_MALE                            1.870
+pathologic_stage_2.0                   3.211
+pathologic_stage_3.0                   4.572
+pathologic_stage_4.0                   5.758
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1843,13 +1928,28 @@
       <c r="B8" t="n">
         <v>2.839</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5.758</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+FAT1group_Low                          0.488
+gender_MALE                            0.858
+pathologic_stage_2.0                   1.274
+pathologic_stage_3.0                   1.776
+pathologic_stage_4.0                   1.400
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+FAT1group_Low                          1.058
+gender_MALE                            1.870
+pathologic_stage_2.0                   3.211
+pathologic_stage_3.0                   4.572
+pathologic_stage_4.0                   5.758
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
@@ -1866,7 +1966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1882,15 +1982,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1905,13 +2000,24 @@
       <c r="B2" t="n">
         <v>1.007</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.027</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+pathologic_stage                       1.280
+FAT1group_Low                          0.465
+gender_MALE                            0.873
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+pathologic_stage                       1.823
+FAT1group_Low                          1.000
+gender_MALE                            1.868
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.462</t>
         </is>
@@ -1926,13 +2032,24 @@
       <c r="B3" t="n">
         <v>1.001</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+pathologic_stage                       1.280
+FAT1group_Low                          0.465
+gender_MALE                            0.873
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+pathologic_stage                       1.823
+FAT1group_Low                          1.000
+gender_MALE                            1.868
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.837</t>
         </is>
@@ -1947,13 +2064,24 @@
       <c r="B4" t="n">
         <v>1.527</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.823</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+pathologic_stage                       1.280
+FAT1group_Low                          0.465
+gender_MALE                            0.873
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+pathologic_stage                       1.823
+FAT1group_Low                          1.000
+gender_MALE                            1.868
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1968,13 +2096,24 @@
       <c r="B5" t="n">
         <v>0.6820000000000001</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+pathologic_stage                       1.280
+FAT1group_Low                          0.465
+gender_MALE                            0.873
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+pathologic_stage                       1.823
+FAT1group_Low                          1.000
+gender_MALE                            1.868
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.050</t>
         </is>
@@ -1989,13 +2128,24 @@
       <c r="B6" t="n">
         <v>1.277</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.868</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>covariate
+age_at_initial_pathologic_diagnosis    0.988
+number_pack_years_smoked               0.993
+pathologic_stage                       1.280
+FAT1group_Low                          0.465
+gender_MALE                            0.873
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age_at_initial_pathologic_diagnosis    1.027
+number_pack_years_smoked               1.008
+pathologic_stage                       1.823
+FAT1group_Low                          1.000
+gender_MALE                            1.868
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.208</t>
         </is>

--- a/result/FAT1_LUAD_Tables.xlsx
+++ b/result/FAT1_LUAD_Tables.xlsx
@@ -1714,23 +1714,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-FAT1group_Low                          0.488
-gender_MALE                            0.858
-pathologic_stage_2.0                   1.274
-pathologic_stage_3.0                   1.776
-pathologic_stage_4.0                   1.400
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-FAT1group_Low                          1.058
-gender_MALE                            1.870
-pathologic_stage_2.0                   3.211
-pathologic_stage_3.0                   4.572
-pathologic_stage_4.0                   5.758
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.988-1.027</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1750,23 +1734,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-FAT1group_Low                          0.488
-gender_MALE                            0.858
-pathologic_stage_2.0                   1.274
-pathologic_stage_3.0                   1.776
-pathologic_stage_4.0                   1.400
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-FAT1group_Low                          1.058
-gender_MALE                            1.870
-pathologic_stage_2.0                   3.211
-pathologic_stage_3.0                   4.572
-pathologic_stage_4.0                   5.758
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.993-1.008</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1786,23 +1754,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-FAT1group_Low                          0.488
-gender_MALE                            0.858
-pathologic_stage_2.0                   1.274
-pathologic_stage_3.0                   1.776
-pathologic_stage_4.0                   1.400
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-FAT1group_Low                          1.058
-gender_MALE                            1.870
-pathologic_stage_2.0                   3.211
-pathologic_stage_3.0                   4.572
-pathologic_stage_4.0                   5.758
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.488-1.058</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1822,23 +1774,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-FAT1group_Low                          0.488
-gender_MALE                            0.858
-pathologic_stage_2.0                   1.274
-pathologic_stage_3.0                   1.776
-pathologic_stage_4.0                   1.400
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-FAT1group_Low                          1.058
-gender_MALE                            1.870
-pathologic_stage_2.0                   3.211
-pathologic_stage_3.0                   4.572
-pathologic_stage_4.0                   5.758
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.858-1.870</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1858,23 +1794,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-FAT1group_Low                          0.488
-gender_MALE                            0.858
-pathologic_stage_2.0                   1.274
-pathologic_stage_3.0                   1.776
-pathologic_stage_4.0                   1.400
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-FAT1group_Low                          1.058
-gender_MALE                            1.870
-pathologic_stage_2.0                   3.211
-pathologic_stage_3.0                   4.572
-pathologic_stage_4.0                   5.758
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>1.274-3.211</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1894,23 +1814,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-FAT1group_Low                          0.488
-gender_MALE                            0.858
-pathologic_stage_2.0                   1.274
-pathologic_stage_3.0                   1.776
-pathologic_stage_4.0                   1.400
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-FAT1group_Low                          1.058
-gender_MALE                            1.870
-pathologic_stage_2.0                   3.211
-pathologic_stage_3.0                   4.572
-pathologic_stage_4.0                   5.758
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>1.776-4.572</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1930,23 +1834,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-FAT1group_Low                          0.488
-gender_MALE                            0.858
-pathologic_stage_2.0                   1.274
-pathologic_stage_3.0                   1.776
-pathologic_stage_4.0                   1.400
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-FAT1group_Low                          1.058
-gender_MALE                            1.870
-pathologic_stage_2.0                   3.211
-pathologic_stage_3.0                   4.572
-pathologic_stage_4.0                   5.758
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>1.400-5.758</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2002,19 +1890,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-pathologic_stage                       1.280
-FAT1group_Low                          0.465
-gender_MALE                            0.873
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-pathologic_stage                       1.823
-FAT1group_Low                          1.000
-gender_MALE                            1.868
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.988-1.027</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2034,19 +1910,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-pathologic_stage                       1.280
-FAT1group_Low                          0.465
-gender_MALE                            0.873
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-pathologic_stage                       1.823
-FAT1group_Low                          1.000
-gender_MALE                            1.868
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.993-1.008</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2066,19 +1930,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-pathologic_stage                       1.280
-FAT1group_Low                          0.465
-gender_MALE                            0.873
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-pathologic_stage                       1.823
-FAT1group_Low                          1.000
-gender_MALE                            1.868
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>1.280-1.823</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2098,19 +1950,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-pathologic_stage                       1.280
-FAT1group_Low                          0.465
-gender_MALE                            0.873
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-pathologic_stage                       1.823
-FAT1group_Low                          1.000
-gender_MALE                            1.868
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.465-1.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2130,19 +1970,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>covariate
-age_at_initial_pathologic_diagnosis    0.988
-number_pack_years_smoked               0.993
-pathologic_stage                       1.280
-FAT1group_Low                          0.465
-gender_MALE                            0.873
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age_at_initial_pathologic_diagnosis    1.027
-number_pack_years_smoked               1.008
-pathologic_stage                       1.823
-FAT1group_Low                          1.000
-gender_MALE                            1.868
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.873-1.868</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/result/FAT1_LUAD_Tables.xlsx
+++ b/result/FAT1_LUAD_Tables.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,25 +875,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PLAURexpression</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SNAI1expression</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>VEGFCexpression</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>EGFRExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
         </is>
@@ -927,25 +947,45 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.218</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.099</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>0.131</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.141</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>-0.004</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>0.017</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>0.041</t>
         </is>
@@ -971,25 +1011,45 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.524</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.852</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>0.004</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.002</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.921</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>0.700</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>0.361</t>
         </is>
@@ -1023,25 +1083,45 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.071</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.007</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>0.011</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>-0.016</t>
         </is>
@@ -1067,25 +1147,45 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.198</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.906</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>0.837</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>0.774</t>
         </is>
@@ -1119,25 +1219,45 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.060</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-0.068</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.086</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.027</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>-0.001</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>-0.022</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0.072</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>-0.048</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>-0.050</t>
         </is>
@@ -1163,25 +1283,45 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.182</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.130</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.057</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.551</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>0.983</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.624</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.112</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>0.291</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>0.265</t>
         </is>
@@ -1190,7 +1330,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EGFRExpression</t>
+          <t>ITGB1expression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1200,17 +1340,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1220,22 +1360,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.202</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-0.099</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-0.120</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-0.091</t>
         </is>
       </c>
     </row>
@@ -1248,45 +1408,65 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.043</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>PLAURexpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,22 +1476,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.068</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1321,17 +1501,37 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>0.341</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>-0.057</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.004</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.080</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>-0.045</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-0.044</t>
         </is>
       </c>
     </row>
@@ -1344,45 +1544,65 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>0.130</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.054</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>0.209</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.934</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.078</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.316</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.326</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>SNAI1expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,27 +1612,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>-0.086</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.057</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1422,12 +1642,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.233</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>0.025</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-0.128</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>-0.070</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.018</t>
         </is>
       </c>
     </row>
@@ -1440,45 +1680,65 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>0.852</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.906</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.587</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.501</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.692</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>VEGFCexpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,32 +1748,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.048</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.233</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1523,7 +1783,27 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-0.058</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-0.102</t>
         </is>
       </c>
     </row>
@@ -1536,45 +1816,65 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.551</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.369</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.024</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1584,42 +1884,62 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>0.131</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.202</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-0.026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0.041</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.016</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-0.050</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-0.123</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>-0.024</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>0.061</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0.080</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.040</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -1632,40 +1952,604 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.983</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.587</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.369</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.595</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.177</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KrasExpression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.141</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.039</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.022</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.482</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.624</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.054</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.501</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0.934</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.078</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TP53Expression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-0.099</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-0.128</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.058</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-0.123</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.921</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.408</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.940</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ALKExpression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-0.048</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-0.120</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-0.045</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-0.070</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-0.024</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.291</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.316</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.595</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.934</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.372</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BRAFExpression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-0.091</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-0.044</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.102</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.061</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>0.361</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.774</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>0.265</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.043</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.326</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>0.177</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0.078</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0.940</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>0.372</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3079,12 +3963,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.572</t>
+          <t>8.452</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.038</t>
         </is>
       </c>
     </row>
@@ -3106,12 +3990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.610</t>
+          <t>4.067</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>0.254</t>
         </is>
       </c>
     </row>
